--- a/resources/templates/7调查了解记录1基本情况表.xlsx
+++ b/resources/templates/7调查了解记录1基本情况表.xlsx
@@ -35,7 +35,7 @@
     <t>被 审 计 单 位 基 本 情 况 表</t>
   </si>
   <si>
-    <t xml:space="preserve">单位名称：                                                          截止：年 月 日                    </t>
+    <t xml:space="preserve">单位名称：{unitName}                          截止：    年    月    日</t>
   </si>
   <si>
     <t>单位性质</t>
